--- a/artfynd/A 19165-2026 artfynd.xlsx
+++ b/artfynd/A 19165-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114569246</v>
+        <v>114571306</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570381</v>
+        <v>570163</v>
       </c>
       <c r="R2" t="n">
-        <v>6765162</v>
+        <v>6765351</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,12 +779,7 @@
         <v>114571305</v>
       </c>
       <c r="B3" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114571306</v>
+        <v>114571307</v>
       </c>
       <c r="B4" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570163</v>
+        <v>570167</v>
       </c>
       <c r="R4" t="n">
-        <v>6765351</v>
+        <v>6765372</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,58 +978,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114566346</v>
+        <v>81760776</v>
       </c>
       <c r="B5" t="n">
-        <v>96616</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fallviken-Grönviken, Gstr</t>
+          <t>Åmot, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570169</v>
+        <v>570414</v>
       </c>
       <c r="R5" t="n">
-        <v>6765375</v>
+        <v>6765208</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,12 +1043,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Ecocom AB</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,56 +1062,50 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mårten Nilsson</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Barbara Kühn, Kajsa Mattsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114571307</v>
+        <v>114564871</v>
       </c>
       <c r="B6" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570167</v>
+        <v>570408</v>
       </c>
       <c r="R6" t="n">
-        <v>6765372</v>
+        <v>6765217</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,12 +1148,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,10 +1184,426 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>81760586</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Åmot, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>570410</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6765210</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-08-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Ecocom AB</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Axel Linder</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Barbara Kühn, Kajsa Mattsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114569219</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fallviken-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>570118</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6765288</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
           <t>Ward Tamsyn</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114566346</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fallviken-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>570169</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6765375</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114569246</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fallviken-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>570381</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6765162</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
